--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -1,122 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bishoymichail/Desktop/Bisho/Uni/Yr5/T1/COMP9417 - Machine Learning/group/COMP9517-Group-Project/ml/bm/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECFD4763-C8D0-8947-9E72-C364FA54BD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="100900" yWindow="-5660" windowWidth="30300" windowHeight="21960" xr2:uid="{7468685A-2FEF-F44B-929D-FB227807A898}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="100900" yWindow="-5660" windowWidth="30300" windowHeight="21960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>run_name</t>
-  </si>
-  <si>
-    <t>model</t>
-  </si>
-  <si>
-    <t>hparams</t>
-  </si>
-  <si>
-    <t>precision</t>
-  </si>
-  <si>
-    <t>recall</t>
-  </si>
-  <si>
-    <t>f1</t>
-  </si>
-  <si>
-    <t>iou</t>
-  </si>
-  <si>
-    <t>train_time_s</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>baseline</t>
-  </si>
-  <si>
-    <t>RandomForest</t>
-  </si>
-  <si>
-    <t>n_estimators=80, max_depth=20, class_weight=balanced_subscample, pixels_per_image=4000</t>
-  </si>
-  <si>
-    <t>eval_time_s</t>
-  </si>
-  <si>
-    <t>reproduction of Chris' baseline, 17 colour features.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="16"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.14999847407452621"/>
+        <fgColor theme="1" tint="0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -133,37 +61,102 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -483,81 +476,925 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A44146-40D5-E144-A962-433CB7B79AF5}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="11" width="21.5" style="3" customWidth="1"/>
+    <col width="21.5" customWidth="1" style="3" min="1" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="85" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="1" ht="23" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>hparams</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>iou</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>train_time_s</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>eval_time_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="85" customHeight="1">
+      <c r="A2" s="6" t="n">
         <v>46129</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.92600000000000005</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.88690000000000002</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.90239999999999998</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.83130000000000004</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>n_estimators=80, max_depth=20, class_weight=balanced_subscample, pixels_per_image=4000</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.9024</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>25.23</v>
       </c>
-      <c r="J2" s="3">
-        <v>6.5892999999999997</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>14</v>
+      <c r="J2" s="3" t="n">
+        <v>6.5893</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>reproduction of Chris' baseline, 17 colour features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:34:48</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>sweep_n100_dNone_msl1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=None, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8972</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8935999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8177</v>
+      </c>
+      <c r="I3" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9078</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:35:44</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sweep_n100_dNone_msl4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=None, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9322</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8803</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="I4" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9170</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:36:37</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sweep_n100_d20_msl1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8871</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8314</v>
+      </c>
+      <c r="I5" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9185</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:37:21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sweep_n100_d20_msl4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=20, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9363</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8307</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9180</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:38:16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sweep_n100_d40_msl1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=40, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8972</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8937</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9082</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:39:24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sweep_n100_d40_msl4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=40, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="I8" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9171</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:41:11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sweep_n200_dNone_msl1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=None, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8973</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8935999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8178</v>
+      </c>
+      <c r="I9" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9081</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:42:51</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sweep_n200_dNone_msl4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=None, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9323</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8808</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="I10" t="n">
+        <v>80.23</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9173</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:44:32</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sweep_n200_d20_msl1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9258</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8875999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9026</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="I11" t="n">
+        <v>82.62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:46:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sweep_n200_d20_msl4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9362</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8312</v>
+      </c>
+      <c r="I12" t="n">
+        <v>101.51</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9183</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:48:35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sweep_n200_d40_msl1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=40, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8962</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8935999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8179</v>
+      </c>
+      <c r="I13" t="n">
+        <v>95.09</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9083</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:50:50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sweep_n200_d40_msl4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=40, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9323</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9026</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8310999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>112.87</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9175</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:54:28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sweep_n400_dNone_msl1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=None, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8974</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8183</v>
+      </c>
+      <c r="I15" t="n">
+        <v>162.34</v>
+      </c>
+      <c r="J15" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9083</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:57:37</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sweep_n400_dNone_msl4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=None, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9324</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8812</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8314</v>
+      </c>
+      <c r="I16" t="n">
+        <v>152.57</v>
+      </c>
+      <c r="J16" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9177</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:00:18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sweep_n400_d20_msl1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9256</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8878</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="I17" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9192</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:02:54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sweep_n400_d20_msl4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=20, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9361</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9024</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8310999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9185</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:06:16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sweep_n400_d40_msl1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=40, min_samples_leaf=1, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8975</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8966</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8184</v>
+      </c>
+      <c r="I19" t="n">
+        <v>153.64</v>
+      </c>
+      <c r="J19" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9086</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-17 16:09:18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sweep_n400_d40_msl4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=40, min_samples_leaf=4, class_weight=balanced_subsample</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9324</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8812</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="I20" t="n">
+        <v>144.66</v>
+      </c>
+      <c r="J20" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>val split, oob=0.9177</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="100900" yWindow="-5660" windowWidth="30300" windowHeight="21960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="103920" yWindow="-5660" windowWidth="27280" windowHeight="21660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -66,23 +66,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="21.5" customWidth="1" style="3" min="1" max="11"/>
+    <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="23" customHeight="1">
@@ -545,43 +545,43 @@
       </c>
     </row>
     <row r="2" ht="85" customHeight="1">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="3" t="n">
         <v>46129</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>n_estimators=80, max_depth=20, class_weight=balanced_subscample, pixels_per_image=4000</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.926</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.8869</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>0.9024</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.8313</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="6" t="n">
         <v>25.23</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>6.5893</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>reproduction of Chris' baseline, 17 colour features.</t>
         </is>
@@ -1394,6 +1394,96 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>val split, oob=0.9177</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:40:07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>multiscale_sigma1248_3ch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample, features=17colour+12multiscale(a_lab,ExG,NGRDI @ sigma=1,2,4,8)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9474</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8798</v>
+      </c>
+      <c r="I21" t="n">
+        <v>141.33</v>
+      </c>
+      <c r="J21" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>val split; oob=0.9456; experiment 2 — multi-scale features</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-19 11:20:20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>multiscale_sigma1248_3ch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample, features=17colour+12multiscale(a_lab,ExG,NGRDI @ sigma=1,2,4,8)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9474</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8798</v>
+      </c>
+      <c r="I22" t="n">
+        <v>262.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>val split; oob=0.9456; experiment 2 — multi-scale features</t>
         </is>
       </c>
     </row>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
@@ -1487,6 +1487,141 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:07:13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ablation_multiscale_a_lab_only</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample, features=17colour+4multiscale(a_lab@sigma=1,2,4,8)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9509</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.8782</v>
+      </c>
+      <c r="I23" t="n">
+        <v>122.91</v>
+      </c>
+      <c r="J23" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>val split; oob=0.9413; ablation - multi-scale a_lab only</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:09:22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ablation_multiscale_exg_only</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample, features=17colour+4multiscale(exg@sigma=1,2,4,8)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9474</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9159</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.8739</v>
+      </c>
+      <c r="I24" t="n">
+        <v>113.03</v>
+      </c>
+      <c r="J24" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>val split; oob=0.9422; ablation - multi-scale exg only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:11:30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ablation_multiscale_ngrdi_only</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample, features=17colour+4multiscale(ngrdi@sigma=1,2,4,8)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9102</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9254</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8673999999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>111.69</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>val split; oob=0.9375; ablation - multi-scale ngrdi only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
@@ -1622,6 +1622,51 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:53:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>final_test_multiscale</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=1, class_weight=balanced_subsample, features=17colour+12multiscale(a_lab,ExG,NGRDI@sigma=1,2,4,8)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9457</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9216</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="I26" t="n">
+        <v>262.25</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>test split (FINAL) - rf_v2 multi-scale, one-shot evaluation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
@@ -1667,6 +1667,231 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:32:49</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sweep_k3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>n_neighbors=3, weights=uniform, algorithm=auto</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9134</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8499</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J27" t="n">
+        <v>154.89</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:35:42</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sweep_k5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>n_neighbors=5, weights=uniform, algorithm=auto</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9464</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8917</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>172.99</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:38:31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sweep_k7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>n_neighbors=7, weights=uniform, algorithm=auto</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9509</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.8895</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9149</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:41:25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sweep_k15</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>n_neighbors=15, weights=uniform, algorithm=auto</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8833</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:44:29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sweep_k31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>n_neighbors=31, weights=uniform, algorithm=auto</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9584</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8756</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.9054</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>183.54</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
@@ -1892,6 +1892,51 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-19 18:39:16</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>feat_compare_17feat_k7</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>n_neighbors=7, weights=uniform, algorithm=auto, features=17colour, pixels_per_image=350</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8446</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J32" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels; compare to sweep_k7 (29 features)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
@@ -1937,6 +1937,51 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:07:48</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>weights_distance_k7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>n_neighbors=7, weights=distance, algorithm=auto, features=17colour+12multiscale(a_lab,ExG,NGRDI@sigma=1,2,4,8), pixels_per_image=350</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8895999999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.9149</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>135.92</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>val split; ~50k training pixels; compare to sweep_k7 (uniform weights)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ml/bm/training_results_history.xlsx
+++ b/ml/bm/training_results_history.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21.5" customWidth="1" style="2" min="1" max="11"/>
@@ -1982,6 +1982,51 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:17:09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>final_test_knn_k7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>n_neighbors=7, weights=uniform, algorithm=auto, features=17colour+12multiscale(a_lab,ExG,NGRDI@sigma=1,2,4,8), pixels_per_image=350</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9474</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8967000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9195</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>178.97</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>test split (FINAL) - kNN k=7 uniform, 29 features, one-shot evaluation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
